--- a/docs/签到表.xlsx
+++ b/docs/签到表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A_Senior\C_软件工程实践\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A_Senior\C_软件工程实践\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41F5EDFD-B260-4E85-BF47-505E53DE222C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E952D69-91C4-453E-875C-90CC6C0A6348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9670" yWindow="2550" windowWidth="11930" windowHeight="12640" xr2:uid="{052747DC-6BAE-464D-9B40-33BBC39E1DCC}"/>
+    <workbookView xWindow="11870" yWindow="2640" windowWidth="11930" windowHeight="12640" xr2:uid="{052747DC-6BAE-464D-9B40-33BBC39E1DCC}"/>
   </bookViews>
   <sheets>
     <sheet name="签到表" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>陈怡冰</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -64,24 +64,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>w1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w2</t>
-  </si>
-  <si>
-    <t>w3</t>
-  </si>
-  <si>
-    <t>w4</t>
-  </si>
-  <si>
     <t>请假（有假条）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>实习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w1-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w2-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w2-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w3-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w3-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w4-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w4-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -143,12 +162,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,105 +486,175 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EF42C10-0C4A-438C-A141-FE882ADE3CAB}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="3.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="5.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
